--- a/input/gcamdata/St14_data.xlsx
+++ b/input/gcamdata/St14_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claudia.rodes\Documents\IAM_COMPACT\gcam-core-iamcompact\input\gcamdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC299C4-06B3-4388-8A3A-E31778DE20D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DDCCF4-B088-4221-9722-2FF43ACC93FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="822" activeTab="4" xr2:uid="{BB24ACD2-C62D-45CA-BD90-8F4156D716B2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="822" activeTab="2" xr2:uid="{BB24ACD2-C62D-45CA-BD90-8F4156D716B2}"/>
   </bookViews>
   <sheets>
     <sheet name="TRN-LoadFactor-computation" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="222">
   <si>
     <t>Country</t>
   </si>
@@ -695,9 +695,6 @@
     <t>Percentage 2050</t>
   </si>
   <si>
-    <t>EU-27</t>
-  </si>
-  <si>
     <t>Factor computation</t>
   </si>
   <si>
@@ -719,12 +716,6 @@
     <t>int av</t>
   </si>
   <si>
-    <t>GDP 2020 y 2050, ver cambio relativo d GDP, ver cambio relativo 2050-2020 de passkm</t>
-  </si>
-  <si>
-    <t>a-0.34/subida GDP</t>
-  </si>
-  <si>
     <t>pass km/year</t>
   </si>
   <si>
@@ -738,6 +729,9 @@
   </si>
   <si>
     <t>tranSubsector</t>
+  </si>
+  <si>
+    <t>energy.final.demand</t>
   </si>
 </sst>
 </file>
@@ -3154,7 +3148,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D873F629-471C-4615-9490-522A722B073D}">
-  <dimension ref="A1:AC372"/>
+  <dimension ref="A1:AC342"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -12687,7 +12681,7 @@
         <v>30046.097194000002</v>
       </c>
       <c r="M241" s="48" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.3">
@@ -12725,7 +12719,7 @@
         <v>20356.115123200001</v>
       </c>
       <c r="M242" s="48" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.3">
@@ -12748,7 +12742,7 @@
         <v>153</v>
       </c>
       <c r="H243" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I243">
         <v>12</v>
@@ -12763,7 +12757,7 @@
         <v>181455.60719000001</v>
       </c>
       <c r="M243" s="48" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.3">
@@ -12786,7 +12780,7 @@
         <v>153</v>
       </c>
       <c r="H244" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I244">
         <v>13</v>
@@ -12801,7 +12795,7 @@
         <v>183841.65023999999</v>
       </c>
       <c r="M244" s="48" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.3">
@@ -12845,7 +12839,7 @@
         <v>153</v>
       </c>
       <c r="H246" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.3">
@@ -12868,7 +12862,7 @@
         <v>153</v>
       </c>
       <c r="H247" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I247">
         <v>12</v>
@@ -12898,7 +12892,7 @@
         <v>153</v>
       </c>
       <c r="H248" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I248">
         <v>13</v>
@@ -13420,13 +13414,13 @@
         <v>2050</v>
       </c>
       <c r="E283" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F283" s="12" t="s">
         <v>156</v>
       </c>
       <c r="G283" s="40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J283">
         <v>2015</v>
@@ -13458,10 +13452,10 @@
         <v>167</v>
       </c>
       <c r="G284" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H284" s="50" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I284" s="11" t="s">
         <v>168</v>
@@ -13507,7 +13501,7 @@
     </row>
     <row r="286" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B286">
         <f>H6</f>
@@ -13540,7 +13534,7 @@
     </row>
     <row r="287" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B287">
         <f>H13+H14+H15+H16+H18+H19+H21+H22</f>
@@ -13603,7 +13597,7 @@
     </row>
     <row r="290" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B290">
         <f>H26</f>
@@ -13636,7 +13630,7 @@
     </row>
     <row r="291" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B291">
         <f>H33+H34+H35+H36+H38+H39+H41+H42</f>
@@ -13653,9 +13647,6 @@
     </row>
     <row r="293" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A293" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="I293" t="s">
         <v>218</v>
       </c>
     </row>
@@ -13676,9 +13667,6 @@
         <f>(D294-B294)/B294</f>
         <v>1.0136011249237815</v>
       </c>
-      <c r="I294" t="s">
-        <v>217</v>
-      </c>
     </row>
     <row r="295" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A295" s="25" t="s">
@@ -13764,7 +13752,7 @@
         <v>156</v>
       </c>
       <c r="L301" s="40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O301">
         <v>2015</v>
@@ -13791,7 +13779,7 @@
         <v>2050</v>
       </c>
       <c r="W301" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.3">
@@ -13799,7 +13787,7 @@
         <v>167</v>
       </c>
       <c r="L302" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N302" s="11" t="s">
         <v>174</v>
@@ -15713,775 +15701,17 @@
       <c r="R333" s="13"/>
       <c r="S333" s="13"/>
     </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B334" s="13"/>
-      <c r="C334" s="13"/>
-      <c r="D334" s="13"/>
-      <c r="E334" s="13"/>
-      <c r="F334" s="13"/>
-      <c r="G334" s="13"/>
-      <c r="H334" s="13"/>
-      <c r="I334" s="13"/>
-      <c r="L334" s="13"/>
-      <c r="M334" s="13"/>
-      <c r="N334" s="13"/>
-      <c r="O334" s="13"/>
-      <c r="P334" s="13"/>
-      <c r="Q334" s="13"/>
-      <c r="R334" s="13"/>
-      <c r="S334" s="13"/>
-    </row>
     <row r="335" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A335" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="B335" s="13"/>
-      <c r="C335" s="13"/>
-      <c r="D335" s="13"/>
-      <c r="E335" s="13"/>
-      <c r="F335" s="13"/>
-      <c r="G335" s="13"/>
-      <c r="H335" s="13"/>
-      <c r="I335" s="13"/>
-      <c r="L335" s="13"/>
-      <c r="M335" s="13"/>
-      <c r="N335" s="13"/>
-      <c r="O335" s="13"/>
-      <c r="P335" s="13"/>
-      <c r="Q335" s="13"/>
-      <c r="R335" s="13"/>
-      <c r="S335" s="13"/>
+      <c r="A335" s="12"/>
     </row>
     <row r="336" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A336" t="s">
-        <v>203</v>
-      </c>
-      <c r="B336" s="13">
-        <f>B329+B313</f>
-        <v>217699.30000000002</v>
-      </c>
-      <c r="C336" s="13">
-        <f t="shared" ref="C336:I336" si="35">C329+C313</f>
-        <v>212500.90000000002</v>
-      </c>
-      <c r="D336" s="13">
-        <f t="shared" si="35"/>
-        <v>194902.40000000002</v>
-      </c>
-      <c r="E336" s="13">
-        <f t="shared" si="35"/>
-        <v>184374.80000000002</v>
-      </c>
-      <c r="F336" s="13">
-        <f t="shared" si="35"/>
-        <v>175777.4</v>
-      </c>
-      <c r="G336" s="13">
-        <f t="shared" si="35"/>
-        <v>169479.83000000002</v>
-      </c>
-      <c r="H336" s="13">
-        <f t="shared" si="35"/>
-        <v>163629.02000000002</v>
-      </c>
-      <c r="I336" s="13">
-        <f t="shared" si="35"/>
-        <v>158102.87</v>
-      </c>
-      <c r="J336" s="39">
-        <f>I336/I$340</f>
-        <v>1.7074171174739208E-2</v>
-      </c>
-      <c r="L336" s="13"/>
-      <c r="M336" s="13"/>
-      <c r="N336" s="13"/>
-      <c r="O336" s="13"/>
-      <c r="P336" s="13"/>
-      <c r="Q336" s="13"/>
-      <c r="R336" s="13"/>
-      <c r="S336" s="13"/>
-    </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A337" t="s">
-        <v>204</v>
-      </c>
-      <c r="B337" s="13">
-        <f t="shared" ref="B337:I340" si="36">B330+B314</f>
-        <v>6611448.7000000002</v>
-      </c>
-      <c r="C337" s="13">
-        <f t="shared" si="36"/>
-        <v>6811059.4299999988</v>
-      </c>
-      <c r="D337" s="13">
-        <f t="shared" si="36"/>
-        <v>7304897.709999999</v>
-      </c>
-      <c r="E337" s="13">
-        <f t="shared" si="36"/>
-        <v>7496899.0699999984</v>
-      </c>
-      <c r="F337" s="13">
-        <f t="shared" si="36"/>
-        <v>7664319.6599999983</v>
-      </c>
-      <c r="G337" s="13">
-        <f t="shared" si="36"/>
-        <v>7729408.6099999994</v>
-      </c>
-      <c r="H337" s="13">
-        <f t="shared" si="36"/>
-        <v>7827854.2300000004</v>
-      </c>
-      <c r="I337" s="13">
-        <f t="shared" si="36"/>
-        <v>7958399.0500000007</v>
-      </c>
-      <c r="J337" s="39">
-        <f t="shared" ref="J337:J339" si="37">I337/I$340</f>
-        <v>0.85945984191546876</v>
-      </c>
-      <c r="L337" s="13"/>
-      <c r="M337" s="13"/>
-      <c r="N337" s="13"/>
-      <c r="O337" s="13"/>
-      <c r="P337" s="13"/>
-      <c r="Q337" s="13"/>
-      <c r="R337" s="13"/>
-      <c r="S337" s="13"/>
-    </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A338" t="s">
-        <v>205</v>
-      </c>
-      <c r="B338" s="13">
-        <f t="shared" si="36"/>
-        <v>444624</v>
-      </c>
-      <c r="C338" s="13">
-        <f t="shared" si="36"/>
-        <v>459901.38500000001</v>
-      </c>
-      <c r="D338" s="13">
-        <f t="shared" si="36"/>
-        <v>511603.67499999999</v>
-      </c>
-      <c r="E338" s="13">
-        <f t="shared" si="36"/>
-        <v>529289.61</v>
-      </c>
-      <c r="F338" s="13">
-        <f t="shared" si="36"/>
-        <v>542650.80000000005</v>
-      </c>
-      <c r="G338" s="13">
-        <f t="shared" si="36"/>
-        <v>544946.39</v>
-      </c>
-      <c r="H338" s="13">
-        <f t="shared" si="36"/>
-        <v>551789.18999999994</v>
-      </c>
-      <c r="I338" s="13">
-        <f t="shared" si="36"/>
-        <v>562691.41</v>
-      </c>
-      <c r="J338" s="39">
-        <f t="shared" si="37"/>
-        <v>6.0767331123687776E-2</v>
-      </c>
-      <c r="L338" s="13"/>
-      <c r="M338" s="13"/>
-      <c r="N338" s="13"/>
-      <c r="O338" s="13"/>
-      <c r="P338" s="13"/>
-      <c r="Q338" s="13"/>
-      <c r="R338" s="13"/>
-      <c r="S338" s="13"/>
-    </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A339" t="s">
-        <v>206</v>
-      </c>
-      <c r="B339" s="13">
-        <f t="shared" si="36"/>
-        <v>283380.59000000003</v>
-      </c>
-      <c r="C339" s="13">
-        <f t="shared" si="36"/>
-        <v>296088.53999999998</v>
-      </c>
-      <c r="D339" s="13">
-        <f t="shared" si="36"/>
-        <v>389767.3</v>
-      </c>
-      <c r="E339" s="13">
-        <f t="shared" si="36"/>
-        <v>453240.3</v>
-      </c>
-      <c r="F339" s="13">
-        <f t="shared" si="36"/>
-        <v>490198.37920000002</v>
-      </c>
-      <c r="G339" s="13">
-        <f t="shared" si="36"/>
-        <v>525270.43070000003</v>
-      </c>
-      <c r="H339" s="13">
-        <f t="shared" si="36"/>
-        <v>554691.03200000001</v>
-      </c>
-      <c r="I339" s="13">
-        <f t="shared" si="36"/>
-        <v>580575.02899999998</v>
-      </c>
-      <c r="J339" s="39">
-        <f t="shared" si="37"/>
-        <v>6.2698655786104202E-2</v>
-      </c>
-      <c r="L339" s="13"/>
-      <c r="M339" s="13"/>
-      <c r="N339" s="13"/>
-      <c r="O339" s="13"/>
-      <c r="P339" s="13"/>
-      <c r="Q339" s="13"/>
-      <c r="R339" s="13"/>
-      <c r="S339" s="13"/>
-    </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A340" t="s">
-        <v>207</v>
-      </c>
-      <c r="B340" s="13">
-        <f t="shared" si="36"/>
-        <v>7557152.5899999999</v>
-      </c>
-      <c r="C340" s="13">
-        <f t="shared" si="36"/>
-        <v>7779550.254999999</v>
-      </c>
-      <c r="D340" s="13">
-        <f t="shared" si="36"/>
-        <v>8401171.084999999</v>
-      </c>
-      <c r="E340" s="13">
-        <f t="shared" si="36"/>
-        <v>8663803.7799999993</v>
-      </c>
-      <c r="F340" s="13">
-        <f t="shared" si="36"/>
-        <v>8872946.2391999979</v>
-      </c>
-      <c r="G340" s="13">
-        <f t="shared" si="36"/>
-        <v>8969105.2606999986</v>
-      </c>
-      <c r="H340" s="13">
-        <f t="shared" si="36"/>
-        <v>9097963.472000001</v>
-      </c>
-      <c r="I340" s="13">
-        <f t="shared" si="36"/>
-        <v>9259768.3590000011</v>
-      </c>
-      <c r="J340" s="39">
-        <f>SUM(J336:J339)</f>
-        <v>1</v>
-      </c>
-      <c r="L340" s="13"/>
-      <c r="M340" s="13"/>
-      <c r="N340" s="13"/>
-      <c r="O340" s="13"/>
-      <c r="P340" s="13"/>
-      <c r="Q340" s="13"/>
-      <c r="R340" s="13"/>
-      <c r="S340" s="13"/>
-    </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B341" s="13"/>
-      <c r="C341" s="13"/>
-      <c r="D341" s="13"/>
-      <c r="E341" s="13"/>
-      <c r="F341" s="13"/>
-      <c r="G341" s="13"/>
-      <c r="H341" s="13"/>
-      <c r="I341" s="13"/>
-      <c r="L341" s="13"/>
-      <c r="M341" s="13"/>
-      <c r="N341" s="13"/>
-      <c r="O341" s="13"/>
-      <c r="P341" s="13"/>
-      <c r="Q341" s="13"/>
-      <c r="R341" s="13"/>
-      <c r="S341" s="13"/>
-    </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A346" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B346">
-        <v>2015</v>
-      </c>
-      <c r="C346">
-        <v>2020</v>
-      </c>
-      <c r="D346">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A347" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="F347" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A348" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="F348" s="25" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
-        <v>64</v>
-      </c>
-      <c r="B349">
-        <f>D257</f>
-        <v>0.85451866970627199</v>
-      </c>
-      <c r="C349">
-        <f>D261</f>
-        <v>0.85738512213416795</v>
-      </c>
-      <c r="D349">
-        <f>D265</f>
-        <v>0.80970254839622502</v>
-      </c>
-      <c r="F349" t="s">
-        <v>64</v>
-      </c>
-      <c r="H349">
-        <f>(C349-B349)/B349</f>
-        <v>3.354464366332991E-3</v>
-      </c>
-      <c r="I349">
-        <f>(D349-B349)/B349</f>
-        <v>-5.2446041144369432E-2</v>
-      </c>
-    </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A350" t="s">
-        <v>65</v>
-      </c>
-      <c r="B350">
-        <f>D269</f>
-        <v>0.84801381692573397</v>
-      </c>
-      <c r="C350">
-        <f>D273</f>
-        <v>0.84736636684584998</v>
-      </c>
-      <c r="D350">
-        <f>D277</f>
-        <v>0.74423346027120296</v>
-      </c>
-      <c r="F350" t="s">
-        <v>65</v>
-      </c>
-      <c r="H350">
-        <f t="shared" ref="H350:H359" si="38">(C350-B350)/B350</f>
-        <v>-7.6349001273487926E-4</v>
-      </c>
-      <c r="I350">
-        <f t="shared" ref="I350:I359" si="39">(D350-B350)/B350</f>
-        <v>-0.12238050204271579</v>
-      </c>
-    </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A351" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="F351" s="25" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A352" t="s">
-        <v>64</v>
-      </c>
-      <c r="B352">
-        <f>D255</f>
-        <v>8.2349165068679203E-2</v>
-      </c>
-      <c r="C352">
-        <f>D259</f>
-        <v>8.22897302938395E-2</v>
-      </c>
-      <c r="D352">
-        <f>D263</f>
-        <v>8.2552391098090802E-2</v>
-      </c>
-      <c r="F352" t="s">
-        <v>64</v>
-      </c>
-      <c r="H352">
-        <f t="shared" si="38"/>
-        <v>-7.2174107400038343E-4</v>
-      </c>
-      <c r="I352">
-        <f t="shared" si="39"/>
-        <v>2.4678578008909798E-3</v>
-      </c>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A353" t="s">
-        <v>65</v>
-      </c>
-      <c r="B353">
-        <f>D267</f>
-        <v>5.96257617654165E-2</v>
-      </c>
-      <c r="C353">
-        <f>D271</f>
-        <v>5.9431937126332803E-2</v>
-      </c>
-      <c r="D353">
-        <f>D275</f>
-        <v>9.76030833468325E-2</v>
-      </c>
-      <c r="F353" t="s">
-        <v>65</v>
-      </c>
-      <c r="H353">
-        <f t="shared" si="38"/>
-        <v>-3.2506861689458187E-3</v>
-      </c>
-      <c r="I353">
-        <f t="shared" si="39"/>
-        <v>0.63692807365428417</v>
-      </c>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A354" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="F354" s="25" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A355" t="s">
-        <v>64</v>
-      </c>
-      <c r="B355">
-        <f>D258</f>
-        <v>6.0547951969845401E-2</v>
-      </c>
-      <c r="C355">
-        <f>D262</f>
-        <v>5.6786681016208498E-2</v>
-      </c>
-      <c r="D355">
-        <f>D266</f>
-        <v>0.107745060505684</v>
-      </c>
-      <c r="F355" t="s">
-        <v>64</v>
-      </c>
-      <c r="H355">
-        <f t="shared" si="38"/>
-        <v>-6.2120531434492157E-2</v>
-      </c>
-      <c r="I355">
-        <f t="shared" si="39"/>
-        <v>0.77949966927608216</v>
-      </c>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A356" t="s">
-        <v>65</v>
-      </c>
-      <c r="B356">
-        <f>D270</f>
-        <v>7.7201177660250406E-2</v>
-      </c>
-      <c r="C356">
-        <f>D274</f>
-        <v>7.8734011034825302E-2</v>
-      </c>
-      <c r="D356">
-        <f>D278</f>
-        <v>0.15375152160556299</v>
-      </c>
-      <c r="F356" t="s">
-        <v>65</v>
-      </c>
-      <c r="H356">
-        <f t="shared" si="38"/>
-        <v>1.9855051710747754E-2</v>
-      </c>
-      <c r="I356">
-        <f t="shared" si="39"/>
-        <v>0.99156964006686488</v>
-      </c>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A357" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="F357" s="25" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A358" t="s">
-        <v>64</v>
-      </c>
-      <c r="B358">
-        <f>D256</f>
-        <v>2.5842132552034002E-3</v>
-      </c>
-      <c r="C358">
-        <f>D260</f>
-        <v>3.5384665557838401E-3</v>
-      </c>
-      <c r="D358">
-        <f>D264</f>
-        <v>0</v>
-      </c>
-      <c r="F358" t="s">
-        <v>64</v>
-      </c>
-      <c r="H358">
-        <f t="shared" si="38"/>
-        <v>0.3692625980688779</v>
-      </c>
-      <c r="I358">
-        <f t="shared" si="39"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A359" t="s">
-        <v>65</v>
-      </c>
-      <c r="B359">
-        <f>D268</f>
-        <v>1.5159243648599101E-2</v>
-      </c>
-      <c r="C359">
-        <f>D272</f>
-        <v>1.44676849929924E-2</v>
-      </c>
-      <c r="D359">
-        <f>D276</f>
-        <v>4.4119347764012603E-3</v>
-      </c>
-      <c r="F359" t="s">
-        <v>65</v>
-      </c>
-      <c r="H359">
-        <f t="shared" si="38"/>
-        <v>-4.5619601586825174E-2</v>
-      </c>
-      <c r="I359">
-        <f t="shared" si="39"/>
-        <v>-0.70896075828895477</v>
-      </c>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A362" s="12" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A363" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A364" t="s">
-        <v>64</v>
-      </c>
-      <c r="C364" t="e">
-        <f>#REF!*(1+#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D364" t="e">
-        <f>#REF!*(1+#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A365" t="s">
-        <v>65</v>
-      </c>
-      <c r="C365" t="e">
-        <f>B342*(1+#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D365" t="e">
-        <f>B342*(1+#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A366" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A367" t="s">
-        <v>64</v>
-      </c>
-      <c r="C367" t="e">
-        <f>C364/#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D367" t="e">
-        <f>D364/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A368" t="s">
-        <v>65</v>
-      </c>
-      <c r="C368" t="e">
-        <f>C365/C342</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D368" t="e">
-        <f>D365/D342</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A369" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B370">
-        <v>2015</v>
-      </c>
-      <c r="C370">
-        <v>2020</v>
-      </c>
-      <c r="D370">
-        <v>2025</v>
-      </c>
-      <c r="E370">
-        <v>2030</v>
-      </c>
-      <c r="F370">
-        <v>2035</v>
-      </c>
-      <c r="G370">
-        <v>2040</v>
-      </c>
-      <c r="H370">
-        <v>2045</v>
-      </c>
-      <c r="I370">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A371" t="s">
-        <v>64</v>
-      </c>
-      <c r="B371">
-        <v>1</v>
-      </c>
-      <c r="C371" t="e">
-        <f>C367</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D371" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C371 + (#REF! -#REF!) * ($I371 - $C371) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E371" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C371 + (#REF! -#REF!) * ($I371 - $C371) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F371" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C371 + (#REF! -#REF!) * ($I371 - $C371) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G371" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C371 + (#REF! -#REF!) * ($I371 - $C371) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H371" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C371 + (#REF! -#REF!) * ($I371 - $C371) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I371" t="e">
-        <f>D367</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A372" t="s">
-        <v>65</v>
-      </c>
-      <c r="B372">
-        <v>1</v>
-      </c>
-      <c r="C372" t="e">
-        <f>C368</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D372" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C372 + (#REF! -#REF!) * ($I372 - $C372) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E372" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C372 + (#REF! -#REF!) * ($I372 - $C372) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F372" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C372 + (#REF! -#REF!) * ($I372 - $C372) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G372" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C372 + (#REF! -#REF!) * ($I372 - $C372) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H372" t="e">
-        <f>IF(#REF!&lt;#REF!,
-   $C372 + (#REF! -#REF!) * ($I372 - $C372) / (#REF! -#REF!),
-   "")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I372" t="e">
-        <f>D368</f>
-        <v>#REF!</v>
-      </c>
+      <c r="A336" s="11"/>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A339" s="11"/>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A342" s="11"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:S45">
@@ -16499,10 +15729,13 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>73</v>
+      </c>
       <c r="B1" cm="1">
         <f t="array" ref="B1:I1">'TRN-Modes-computation'!J283:Q283</f>
         <v>2015</v>
@@ -16528,8 +15761,11 @@
       <c r="I1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:I2">'TRN-Modes-computation'!I285:Q285</f>
         <v>EU-12</v>
@@ -16558,8 +15794,11 @@
       <c r="I2">
         <v>0.13131755632157877</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="str" cm="1">
         <f t="array" ref="A3:I3">'TRN-Modes-computation'!I289:Q289</f>
         <v>EU-15</v>
@@ -16588,9 +15827,13 @@
       <c r="I3">
         <v>-1.5077826179735208</v>
       </c>
+      <c r="J3" t="s">
+        <v>115</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16634,7 +15877,7 @@
         <v>2050</v>
       </c>
       <c r="K1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -17394,7 +16637,7 @@
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B3" s="7">
         <v>2050</v>
@@ -17572,7 +16815,7 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" s="43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B5" s="7">
         <v>2020</v>
@@ -17750,7 +16993,7 @@
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" s="43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B7" s="7">
         <v>2015</v>
